--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/4609-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/4609-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{187BFE27-1ADA-4A83-835B-CA9CAA1EC818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{330B7372-7C3E-413D-8067-C532701BDBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{C4B829A0-835B-447B-BEA1-91BF6C4CAD77}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{4F90842E-893F-41FD-BEE7-A664AC60CA9D}"/>
   </bookViews>
   <sheets>
     <sheet name="4609-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1436,27 +1436,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1CCFE23-9C84-4F62-A8F1-8627A378BB58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9941BAE8-C5F6-4CCC-894A-C2C4798BFCD9}">
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="4" width="6.625" customWidth="1"/>
-    <col min="5" max="5" width="6.25" customWidth="1"/>
-    <col min="6" max="6" width="6.625" customWidth="1"/>
-    <col min="7" max="9" width="6.25" customWidth="1"/>
-    <col min="10" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1490,7 +1489,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1526,7 +1525,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1578,7 +1577,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1646,7 +1645,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2024</v>
       </c>
@@ -1718,7 +1717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2023</v>
       </c>
@@ -1790,7 +1789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2022</v>
       </c>
@@ -1862,7 +1861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2021</v>
       </c>
@@ -1934,7 +1933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2020</v>
       </c>
@@ -2006,7 +2005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2019</v>
       </c>
@@ -2078,7 +2077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2018</v>
       </c>
@@ -2150,7 +2149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2017</v>
       </c>
@@ -2222,7 +2221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2016</v>
       </c>
@@ -2294,7 +2293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2015</v>
       </c>
@@ -2366,7 +2365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2014</v>
       </c>
@@ -2438,7 +2437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2013</v>
       </c>
@@ -2510,7 +2509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2012</v>
       </c>
@@ -2582,7 +2581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2011</v>
       </c>
@@ -2654,7 +2653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2010</v>
       </c>
@@ -2726,7 +2725,7 @@
         <v>7.74</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2009</v>
       </c>
@@ -2798,7 +2797,7 @@
         <v>9.7899999999999991</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>2008</v>
       </c>
@@ -2870,7 +2869,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2007</v>
       </c>
@@ -2942,7 +2941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
         <v>2006</v>
       </c>
@@ -3014,7 +3013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2005</v>
       </c>
@@ -3086,7 +3085,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="33">
         <v>2004</v>
       </c>
@@ -3158,7 +3157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2003</v>
       </c>
@@ -3230,7 +3229,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>2002</v>
       </c>
@@ -3302,7 +3301,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2001</v>
       </c>
@@ -3374,7 +3373,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>2000</v>
       </c>
@@ -3446,7 +3445,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>1999</v>
       </c>
@@ -3518,7 +3517,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
         <v>1998</v>
       </c>
@@ -3590,7 +3589,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>1997</v>
       </c>
@@ -3662,7 +3661,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="33" t="s">
         <v>38</v>
       </c>
